--- a/data/merged/2026-09-23/MERGED_IT_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_IT_Mite-Vacuum_2026-09-23.xlsx
@@ -3297,13 +3297,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3341,13 +3341,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3561,13 +3561,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3649,13 +3649,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3737,13 +3737,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3957,13 +3957,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4024,94 +4024,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId34" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Product 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Product 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId36" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4453,7 +4365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR37"/>
+  <dimension ref="A1:BR35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6568,7 +6480,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -6581,23 +6493,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO Galleggiante per Lavasciuga Pavimenti Filtro per Serbatoio di Scarico Acciaio Inossidabile Parte Accessori Facile In</t>
+          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8W81X7Y?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -6617,9 +6529,13 @@
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
-      <c r="AD18" s="20"/>
+      <c r="AD18" s="20">
+        <v>2</v>
+      </c>
       <c r="AE18"/>
-      <c r="AF18" s="21"/>
+      <c r="AF18" s="21">
+        <v>2.5</v>
+      </c>
       <c r="AG18" s="22">
         <v>0</v>
       </c>
@@ -6670,7 +6586,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FBRWMG4G</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -6683,23 +6599,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
+          <t>Elecbee Battimaterasso Antiacaro, Pulisci Materasso Senza Filo, Aspirapolvere per Materassi, Sterilizzazione UV, Ideale per M</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FBRWMG4G?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71PlgJw046L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FBRWMG4G</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -6720,11 +6636,11 @@
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -6776,7 +6692,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0FBRWMG4G</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -6789,23 +6705,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Battimaterasso Antiacaro, Pulisci Materasso Senza Filo, Aspirapolvere per Materassi, Sterilizzazione UV, Ideale per M</t>
+          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FBRWMG4G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71PlgJw046L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0FBRWMG4G</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -6826,11 +6742,11 @@
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -6882,7 +6798,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -6895,23 +6811,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore Floreale Delight (Plant Essential Oil)</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -6932,11 +6848,11 @@
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -6988,7 +6904,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -7001,23 +6917,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
+          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -7038,11 +6954,11 @@
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -7094,7 +7010,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -7107,23 +7023,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -7144,11 +7060,11 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -7200,7 +7116,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -7213,23 +7129,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
+          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -7250,11 +7166,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -7306,7 +7222,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -7319,23 +7235,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
+          <t>KÄRCHER aspirapolvere per materassi VCH 4 UVClean, pulizia profonda igienica con luce UV-C, rullo battente e funzione aspiran</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61px9qUli6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -7356,11 +7272,11 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>1</v>
+        <v>194</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -7412,7 +7328,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -7425,23 +7341,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
+          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -7462,11 +7378,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -7518,7 +7434,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -7531,23 +7447,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER aspirapolvere per materassi VCH 4 UVClean, pulizia profonda igienica con luce UV-C, rullo battente e funzione aspiran</t>
+          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FPQMRBYZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61px9qUli6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -7568,11 +7484,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>194</v>
+        <v>3</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -7624,7 +7540,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -7637,23 +7553,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
+          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -7674,11 +7590,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -7730,7 +7646,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -7743,23 +7659,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
+          <t>Aspirapolvere per Materassi,Aspira Materasso Antiacaro con Una Forte Potenza di Aspirazione, Aspira Acari per Materassi e Div</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GHQLQBYD?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -7780,11 +7696,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -7836,7 +7752,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -7849,23 +7765,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -7886,11 +7802,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -7942,7 +7858,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -7955,23 +7871,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere per Materassi,Aspira Materasso Antiacaro con Una Forte Potenza di Aspirazione, Aspira Acari per Materassi e Div</t>
+          <t>Aspirapolvere per acari senza fili per materassi, con luce UV da 253,7 nm, ultrasuoni e battitura con rullo a spazzola, per r</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GHQLQBYD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -7992,11 +7908,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -8048,7 +7964,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -8061,23 +7977,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -8097,13 +8013,9 @@
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
-      <c r="AD32" s="20">
-        <v>28</v>
-      </c>
+      <c r="AD32" s="20"/>
       <c r="AE32"/>
-      <c r="AF32" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AF32" s="21"/>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
@@ -8154,7 +8066,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -8167,23 +8079,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere per acari senza fili per materassi, con luce UV da 253,7 nm, ultrasuoni e battitura con rullo a spazzola, per r</t>
+          <t>JIGOO T600 Aspiratore acaro per materassi, 700 W aspirapolvere acari con luce UV, 15 kpa attrazione acari aspirapolvere antia</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GWD94VPC?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -8199,16 +8111,18 @@
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
       <c r="Y33"/>
-      <c r="Z33" s="19"/>
+      <c r="Z33" s="19">
+        <v>125.35</v>
+      </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>2</v>
+        <v>816</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -8260,7 +8174,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -8273,23 +8187,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
+          <t>Circlio 18 kPa Battimaterasso Antiacaro Senza Fili con Luce UV-C 254 nmsDoppio Contenitore della Polvere | Rimuove il 99% d</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H1HSF3G6?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -8309,9 +8223,13 @@
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
-      <c r="AD34" s="20"/>
+      <c r="AD34" s="20">
+        <v>9</v>
+      </c>
       <c r="AE34"/>
-      <c r="AF34" s="21"/>
+      <c r="AF34" s="21">
+        <v>5</v>
+      </c>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
@@ -8362,7 +8280,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -8375,23 +8293,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore acaro per materassi, 700 W aspirapolvere acari con luce UV, 15 kpa attrazione acari aspirapolvere antia</t>
+          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-CsAspirapolvere per Materassi, Pulizia Profonda, fino al</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GWD94VPC?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -8407,14 +8325,12 @@
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35"/>
-      <c r="Z35" s="19">
-        <v>125.35</v>
-      </c>
+      <c r="Z35" s="19"/>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>816</v>
+        <v>62</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
@@ -8462,218 +8378,6 @@
       <c r="BP35"/>
       <c r="BQ35" s="23"/>
       <c r="BR35"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>B0H1HSF3G6</t>
-        </is>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>Circlio 18 kPa Battimaterasso Antiacaro Senza Fili con Luce UV-C 254 nmsDoppio Contenitore della Polvere | Rimuove il 99% d</t>
-        </is>
-      </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H1HSF3G6?psc=1</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>B0H1HSF3G6</t>
-        </is>
-      </c>
-      <c r="M36" s="1"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36"/>
-      <c r="AD36" s="20">
-        <v>9</v>
-      </c>
-      <c r="AE36"/>
-      <c r="AF36" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36"/>
-      <c r="AI36" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ36"/>
-      <c r="AK36" s="1"/>
-      <c r="AL36" s="20"/>
-      <c r="AM36"/>
-      <c r="AN36" s="13"/>
-      <c r="AO36" s="13"/>
-      <c r="AP36"/>
-      <c r="AQ36" s="20"/>
-      <c r="AR36"/>
-      <c r="AS36"/>
-      <c r="AT36"/>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="13"/>
-      <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
-      <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
-      <c r="BB36" s="13"/>
-      <c r="BC36" s="13"/>
-      <c r="BD36" s="13"/>
-      <c r="BE36" s="13"/>
-      <c r="BF36" s="13"/>
-      <c r="BG36" s="13"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36"/>
-      <c r="BJ36"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36"/>
-      <c r="BM36" s="23"/>
-      <c r="BN36"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36"/>
-      <c r="BQ36" s="23"/>
-      <c r="BR36"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>36</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>B0HFN6BP5R</t>
-        </is>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-CsAspirapolvere per Materassi, Pulizia Profonda, fino al</t>
-        </is>
-      </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L37" s="14" t="inlineStr">
-        <is>
-          <t>B0HFN6BP5R</t>
-        </is>
-      </c>
-      <c r="M37" s="1"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37"/>
-      <c r="Z37" s="19"/>
-      <c r="AA37"/>
-      <c r="AB37"/>
-      <c r="AC37"/>
-      <c r="AD37" s="20">
-        <v>62</v>
-      </c>
-      <c r="AE37"/>
-      <c r="AF37" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH37"/>
-      <c r="AI37" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ37"/>
-      <c r="AK37" s="1"/>
-      <c r="AL37" s="20"/>
-      <c r="AM37"/>
-      <c r="AN37" s="13"/>
-      <c r="AO37" s="13"/>
-      <c r="AP37"/>
-      <c r="AQ37" s="20"/>
-      <c r="AR37"/>
-      <c r="AS37"/>
-      <c r="AT37"/>
-      <c r="AU37" s="13"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="13"/>
-      <c r="AX37" s="13"/>
-      <c r="AY37" s="13"/>
-      <c r="AZ37" s="13"/>
-      <c r="BA37" s="13"/>
-      <c r="BB37" s="13"/>
-      <c r="BC37" s="13"/>
-      <c r="BD37" s="13"/>
-      <c r="BE37" s="13"/>
-      <c r="BF37" s="13"/>
-      <c r="BG37" s="13"/>
-      <c r="BH37" s="14"/>
-      <c r="BI37"/>
-      <c r="BJ37"/>
-      <c r="BK37" s="23"/>
-      <c r="BL37"/>
-      <c r="BM37" s="23"/>
-      <c r="BN37"/>
-      <c r="BO37" s="23"/>
-      <c r="BP37"/>
-      <c r="BQ37" s="23"/>
-      <c r="BR37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8759,108 +8463,98 @@
     <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.it/dp/B0F8HD3649?psc=1"/>
     <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0F8W81X7Y?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0FBRWMG4G?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PlgJw046L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0FBRWMG4G?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PlgJw046L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61px9qUli6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61px9qUli6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0GHQLQBYD?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0GHQLQBYD?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0GWD94VPC?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0H1HSF3G6?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0GWD94VPC?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
-    <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.it/dp/B0H1HSF3G6?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
-    <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
   </hyperlinks>
-  <drawing r:id="rId181"/>
+  <drawing r:id="rId171"/>
 </worksheet>
 </file>
 
